--- a/layout/Layout_REPORTOS_MN_ME_V7.1_2024.xlsx
+++ b/layout/Layout_REPORTOS_MN_ME_V7.1_2024.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/65a63616e5f6ec42/Desktop/DOCUMENTOS_IMPERA/ION/FT_REPORTOS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LOCAL\DESA\non-purple-wheel\non-purple-wheel\layout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{6F9E4785-5F7A-4050-903F-853891BCB92D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEDCD766-2632-4D92-B67B-11645DF29615}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41BA91B2-C402-416B-8943-DFFA40AA498C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="850" yWindow="5580" windowWidth="26520" windowHeight="15950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REPORTOS_MNME" sheetId="2" r:id="rId1"/>
@@ -898,13 +898,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D8BD00A0-63E6-814A-9B3C-338BE91A7B71}" name="Table22567" displayName="Table22567" ref="A1:P46" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
-  <autoFilter ref="A1:P46" xr:uid="{D8BD00A0-63E6-814A-9B3C-338BE91A7B71}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{61A0FC14-9C2C-E94D-A9F6-C09F391A3766}" name="LAYOUT" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{3707FBAC-1D36-AD41-96CD-1A663A59204B}" name="ORDEN" dataDxfId="14"/>
@@ -1225,27 +1220,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A46F6441-ED67-AA45-8F42-548B2B7D4C48}">
   <dimension ref="A1:P46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="18.600000000000001" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="18" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="11.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30.5546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.90625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.90625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.453125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="30.54296875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.54296875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.453125" style="1" customWidth="1"/>
     <col min="7" max="7" width="14" style="1" customWidth="1"/>
-    <col min="8" max="8" width="24.44140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="26.44140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="24.453125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="26.453125" style="1" customWidth="1"/>
     <col min="10" max="10" width="26" style="2" customWidth="1"/>
-    <col min="11" max="11" width="24.5546875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="36.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="32.109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="24.54296875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="36.90625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="32.08984375" style="1" customWidth="1"/>
     <col min="14" max="14" width="34" style="1" customWidth="1"/>
-    <col min="15" max="15" width="21.5546875" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="10.88671875" style="1"/>
+    <col min="15" max="15" width="21.54296875" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="10.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
@@ -1295,7 +1290,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1335,7 +1330,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1371,7 +1366,7 @@
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
     </row>
-    <row r="4" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -1411,7 +1406,7 @@
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
     </row>
-    <row r="5" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A5" s="3" t="s">
         <v>0</v>
       </c>
@@ -1447,7 +1442,7 @@
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
     </row>
-    <row r="6" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
@@ -1483,7 +1478,7 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
     </row>
-    <row r="7" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
@@ -1519,7 +1514,7 @@
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
     </row>
-    <row r="8" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
@@ -1559,7 +1554,7 @@
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
     </row>
-    <row r="9" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
@@ -1595,7 +1590,7 @@
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
     </row>
-    <row r="10" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A10" s="3" t="s">
         <v>0</v>
       </c>
@@ -1631,7 +1626,7 @@
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
     </row>
-    <row r="11" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A11" s="3" t="s">
         <v>0</v>
       </c>
@@ -1667,7 +1662,7 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
     </row>
-    <row r="12" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A12" s="3" t="s">
         <v>0</v>
       </c>
@@ -1703,7 +1698,7 @@
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
     </row>
-    <row r="13" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A13" s="3" t="s">
         <v>0</v>
       </c>
@@ -1743,7 +1738,7 @@
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
     </row>
-    <row r="14" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A14" s="3" t="s">
         <v>0</v>
       </c>
@@ -1779,7 +1774,7 @@
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
     </row>
-    <row r="15" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A15" s="3" t="s">
         <v>0</v>
       </c>
@@ -1815,7 +1810,7 @@
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
     </row>
-    <row r="16" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A16" s="3" t="s">
         <v>0</v>
       </c>
@@ -1851,7 +1846,7 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
     </row>
-    <row r="17" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A17" s="3" t="s">
         <v>0</v>
       </c>
@@ -1891,7 +1886,7 @@
       <c r="O17" s="3"/>
       <c r="P17" s="3"/>
     </row>
-    <row r="18" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A18" s="3" t="s">
         <v>0</v>
       </c>
@@ -1931,7 +1926,7 @@
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
     </row>
-    <row r="19" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A19" s="3" t="s">
         <v>0</v>
       </c>
@@ -1971,7 +1966,7 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
     </row>
-    <row r="20" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A20" s="3" t="s">
         <v>0</v>
       </c>
@@ -2007,7 +2002,7 @@
       <c r="O20" s="3"/>
       <c r="P20" s="3"/>
     </row>
-    <row r="21" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A21" s="3" t="s">
         <v>0</v>
       </c>
@@ -2047,7 +2042,7 @@
       <c r="O21" s="3"/>
       <c r="P21" s="3"/>
     </row>
-    <row r="22" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A22" s="21" t="s">
         <v>0</v>
       </c>
@@ -2089,7 +2084,7 @@
       <c r="O22" s="21"/>
       <c r="P22" s="21"/>
     </row>
-    <row r="23" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A23" s="15" t="s">
         <v>0</v>
       </c>
@@ -2125,7 +2120,7 @@
       <c r="O23" s="15"/>
       <c r="P23" s="15"/>
     </row>
-    <row r="24" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A24" s="3" t="s">
         <v>0</v>
       </c>
@@ -2165,7 +2160,7 @@
       <c r="O24" s="3"/>
       <c r="P24" s="3"/>
     </row>
-    <row r="25" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A25" s="3" t="s">
         <v>0</v>
       </c>
@@ -2205,7 +2200,7 @@
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
     </row>
-    <row r="26" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A26" s="3" t="s">
         <v>0</v>
       </c>
@@ -2245,7 +2240,7 @@
       <c r="O26" s="3"/>
       <c r="P26" s="3"/>
     </row>
-    <row r="27" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A27" s="3" t="s">
         <v>0</v>
       </c>
@@ -2285,7 +2280,7 @@
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
     </row>
-    <row r="28" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A28" s="3" t="s">
         <v>0</v>
       </c>
@@ -2321,7 +2316,7 @@
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
     </row>
-    <row r="29" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A29" s="3" t="s">
         <v>0</v>
       </c>
@@ -2357,7 +2352,7 @@
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
     </row>
-    <row r="30" spans="1:16" ht="37.200000000000003" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:16" ht="36" x14ac:dyDescent="0.5">
       <c r="A30" s="3" t="s">
         <v>0</v>
       </c>
@@ -2393,7 +2388,7 @@
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A31" s="3" t="s">
         <v>0</v>
       </c>
@@ -2431,7 +2426,7 @@
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A32" s="3" t="s">
         <v>0</v>
       </c>
@@ -2465,7 +2460,7 @@
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A33" s="3" t="s">
         <v>0</v>
       </c>
@@ -2503,7 +2498,7 @@
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A34" s="3" t="s">
         <v>0</v>
       </c>
@@ -2537,7 +2532,7 @@
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A35" s="3" t="s">
         <v>0</v>
       </c>
@@ -2571,7 +2566,7 @@
       <c r="O35" s="3"/>
       <c r="P35" s="3"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A36" s="3" t="s">
         <v>0</v>
       </c>
@@ -2605,7 +2600,7 @@
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A37" s="3" t="s">
         <v>0</v>
       </c>
@@ -2643,7 +2638,7 @@
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A38" s="3" t="s">
         <v>0</v>
       </c>
@@ -2681,7 +2676,7 @@
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A39" s="3" t="s">
         <v>0</v>
       </c>
@@ -2715,7 +2710,7 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A40" s="3" t="s">
         <v>0</v>
       </c>
@@ -2753,7 +2748,7 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A41" s="3" t="s">
         <v>0</v>
       </c>
@@ -2791,7 +2786,7 @@
       <c r="O41" s="3"/>
       <c r="P41" s="3"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A42" s="3" t="s">
         <v>0</v>
       </c>
@@ -2829,7 +2824,7 @@
       <c r="O42" s="3"/>
       <c r="P42" s="3"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A43" s="3" t="s">
         <v>0</v>
       </c>
@@ -2867,7 +2862,7 @@
       <c r="O43" s="3"/>
       <c r="P43" s="3"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A44" s="3" t="s">
         <v>0</v>
       </c>
@@ -2905,7 +2900,7 @@
       <c r="O44" s="3"/>
       <c r="P44" s="3"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A45" s="3" t="s">
         <v>0</v>
       </c>
@@ -2947,7 +2942,7 @@
       <c r="O45" s="3"/>
       <c r="P45" s="3"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.5">
       <c r="A46" s="3" t="s">
         <v>0</v>
       </c>
@@ -2992,6 +2987,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cf35dce2-b600-471d-a6b0-9e8301b7851b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3de82841-ffbb-418b-a888-39c303bacd30" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101003EADB6AB950C774BBB9F1C75E500B284" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="101bf262c701ad3b79067f76f13f8957">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cf35dce2-b600-471d-a6b0-9e8301b7851b" xmlns:ns3="3de82841-ffbb-418b-a888-39c303bacd30" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a75b904d2a00e23a3c27f0f1b23bc34b" ns2:_="" ns3:_="">
     <xsd:import namespace="cf35dce2-b600-471d-a6b0-9e8301b7851b"/>
@@ -3192,17 +3198,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cf35dce2-b600-471d-a6b0-9e8301b7851b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3de82841-ffbb-418b-a888-39c303bacd30" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -3213,6 +3208,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E5E09E5-67A3-4C90-83A7-4274DDC3623C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cf35dce2-b600-471d-a6b0-9e8301b7851b"/>
+    <ds:schemaRef ds:uri="3de82841-ffbb-418b-a888-39c303bacd30"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83BD2B94-628C-4FC6-8938-DBECE134A682}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3231,17 +3237,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E5E09E5-67A3-4C90-83A7-4274DDC3623C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cf35dce2-b600-471d-a6b0-9e8301b7851b"/>
-    <ds:schemaRef ds:uri="3de82841-ffbb-418b-a888-39c303bacd30"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F0FB066D-DC24-490D-9537-E3210F529E79}">
   <ds:schemaRefs>
